--- a/LISTAS_ORDENADAS/MA/Tarugos/TARUGOS.xlsx
+++ b/LISTAS_ORDENADAS/MA/Tarugos/TARUGOS.xlsx
@@ -943,7 +943,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45203.55253549859</v>
+        <v>45266</v>
       </c>
       <c r="H1" s="19" t="n"/>
     </row>
@@ -1018,7 +1018,6 @@
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="35.25" customHeight="1" s="22">
       <c r="A10" s="21" t="inlineStr">
         <is>
@@ -1033,27 +1032,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33" ht="27.75" customHeight="1" s="22" thickBot="1">
       <c r="B33" s="38" t="inlineStr">
         <is>
@@ -1144,7 +1122,7 @@
         <v>500</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>1608.2</v>
+        <v>1700</v>
       </c>
       <c r="H37" s="41" t="n"/>
       <c r="J37" s="11" t="n"/>
@@ -1316,9 +1294,6 @@
         <v>5121.6</v>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -1335,11 +1310,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B33:D33"/>
     <mergeCell ref="B40:D40"/>
+    <mergeCell ref="A11:G11"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A11:G11"/>
   </mergeCells>
   <pageMargins left="0.7874015748031497" right="0.7874015748031497" top="0.984251968503937" bottom="0.984251968503937" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
